--- a/web/files/九龙-马头角-南首.xlsx
+++ b/web/files/九龙-马头角-南首.xlsx
@@ -1582,34 +1582,34 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>6756000</v>
+        <v>6620800</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>25885</v>
+        <v>25367</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>6620880</v>
+        <v>6620800</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>25367</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -20576,12 +20576,12 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="P6" s="22" t="inlineStr">
+      <c r="P6" s="20" t="inlineStr">
         <is>
           <t>B9 | 261呎 (1房)
-$676万
-$25,885/呎
-(在售)</t>
+$662万
+$25,367/呎
+(26年-09月-20日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-马头角-南首.xlsx
+++ b/web/files/九龙-马头角-南首.xlsx
@@ -3013,7 +3013,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -20644,7 +20644,7 @@
           <t>A8 | 262呎 (1房)
 $666万
 $25,424/呎
-(26年-08月-24日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">

--- a/web/files/九龙-马头角-南首.xlsx
+++ b/web/files/九龙-马头角-南首.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,17 +125,6 @@
       <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -213,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -279,12 +268,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1644,7 +1627,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2078,7 +2061,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -3938,34 +3921,34 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>6731000</v>
+        <v>6596300</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>25691</v>
+        <v>25177</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>6596380</v>
+        <v>6596300</v>
       </c>
       <c r="L54" s="5" t="n">
         <v>25177</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -20239,22 +20222,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -20512,12 +20495,12 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>A8 | 262呎 (1房)
 $688万
 $26,248/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -20568,12 +20551,12 @@
 (25年-04月-28日)</t>
         </is>
       </c>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t>B8 | 262呎 (1房)
 $645万
 $24,615/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="P6" s="20" t="inlineStr">
@@ -20766,12 +20749,12 @@
 (25年-03月-24日)</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>A8 | 262呎 (1房)
-$673万
-$25,691/呎
-(在售)</t>
+$660万
+$25,177/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">

--- a/web/files/九龙-马头角-南首.xlsx
+++ b/web/files/九龙-马头角-南首.xlsx
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>6877000</v>
+        <v>6739400</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>26248</v>
+        <v>25723</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>6739460</v>
+        <v>6739400</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>25723</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -20495,12 +20495,12 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>A8 | 262呎 (1房)
-$688万
-$26,248/呎
-(在售)</t>
+$674万
+$25,723/呎
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -20564,7 +20564,7 @@
           <t>B9 | 261呎 (1房)
 $662万
 $25,367/呎
-(26年-09月-20日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-马头角-南首.xlsx
+++ b/web/files/九龙-马头角-南首.xlsx
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -16574,14 +16574,14 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
-        <v>4328200</v>
+        <v>3522600</v>
       </c>
       <c r="I258" s="5" t="n">
-        <v>21641</v>
+        <v>17613</v>
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
@@ -16589,10 +16589,10 @@
         </is>
       </c>
       <c r="K258" s="5" t="n">
-        <v>4328200</v>
+        <v>3522600</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>21641</v>
+        <v>17613</v>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
           <t>A8 | 262呎 (1房)
 $660万
 $25,177/呎
-(26年-09月-30日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -22578,9 +22578,9 @@
       <c r="N22" s="20" t="inlineStr">
         <is>
           <t>B7 | 200呎 (开放式)
-$433万
-$21,641/呎
-(25年-03月-21日)</t>
+$352万
+$17,613/呎
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="O22" s="20" t="inlineStr">
